--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:52:35+00:00</t>
+    <t>2026-09-30T09:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:02:48+00:00</t>
+    <t>2026-09-30T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:52:57+00:00</t>
+    <t>2026-10-01T18:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T18:35:17+00:00</t>
+    <t>2026-10-02T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T11:47:48+00:00</t>
+    <t>2026-10-06T07:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -333,7 +333,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.inera.se/ig/ehds-tk/StructureDefinition/inera-ehds-device)
+    <t xml:space="preserve">Reference(https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSDevice)
 </t>
   </si>
   <si>
@@ -667,7 +667,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="63.671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="61.3359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-immunization-registration-device.xlsx
+++ b/StructureDefinition-immunization-registration-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
